--- a/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
+++ b/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
@@ -8,17 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="01-领导一页纸" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02-主亏ID与原因" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03-近周阶段归因" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04-规格搭配（推广前）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05-口径说明" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06-全量ID每周净利润" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07-数据源1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08-周报其他费用" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="02-推广后利率变化" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02-主亏ID与原因" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03-近周阶段归因" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04-规格搭配（推广前）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05-口径说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06-全量ID每周净利润" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="06b-全量ID每周后利率" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="07-数据源1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="08-周报其他费用" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06-全量ID每周净利润'!$A$4:$M$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07-数据源1'!$A$2:$AD$346</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06-全量ID每周净利润'!$A$4:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06b-全量ID每周后利率'!$A$4:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'07-数据源1'!$A$2:$AD$346</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -218,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,6 +291,46 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,6 +495,95 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>推广后利率周趋势</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'02-推广后利率变化'!H11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'02-推广后利率变化'!$A$12:$A$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'02-推广后利率变化'!$H$12:$H$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -459,6 +591,33 @@
       <col>0</col>
       <colOff>0</colOff>
       <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5040000" cy="2520000"/>
@@ -768,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -870,9 +1029,9 @@
           <t>结论3</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>原因要分段：7.6→7.13 主要是推广前利润下降（要看规格搭配）；7.13→7.20 主要是推广费上升（次链/30包加投）。</t>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>原因要分段（看推广后利率）：7.6→7.13 主因推广前利率随量/结构下滑；7.13→7.20 主因推广费率上升（次链/30包加投）。</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -1016,313 +1175,345 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>四、周趋势速览（ID合计）</t>
+          <t>四、周趋势速览（含推广后利率）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>周次</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>成交金额</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>推广前利润</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>推广花费</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>其他费用</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>推广后利润</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>环比_推广后</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>主因</t>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>推广后利率</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>利率环比(pp)</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>主因(利率)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>5.11-5.17</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="43" t="n">
         <v>118254</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="43" t="n">
         <v>15585</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="43" t="n">
         <v>22200</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="44" t="n">
         <v>1911</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="45" t="n">
         <v>-7161</v>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="inlineStr"/>
+      <c r="G25" s="46" t="n">
+        <v>-0.06842813955143394</v>
+      </c>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>5.25-5.31</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="43" t="n">
         <v>123377</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="43" t="n">
         <v>16531</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="43" t="n">
         <v>22867</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="44" t="n">
         <v>1911</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="45" t="n">
         <v>-6845</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>316</v>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>本期改善</t>
+      <c r="G26" s="47" t="n">
+        <v>-0.06269098181676941</v>
+      </c>
+      <c r="H26" s="48" t="n">
+        <v>0.5737157734664531</v>
+      </c>
+      <c r="I26" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>6.15-6.21</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="43" t="n">
         <v>102108</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="43" t="n">
         <v>13774</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="43" t="n">
         <v>19490</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="44" t="n">
         <v>3605</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="45" t="n">
         <v>-8013</v>
       </c>
-      <c r="G27" s="14" t="n">
-        <v>-1168</v>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>推广前利润下降</t>
+      <c r="G27" s="47" t="n">
+        <v>-0.08867717036192986</v>
+      </c>
+      <c r="H27" s="50" t="n">
+        <v>-2.598618854516045</v>
+      </c>
+      <c r="I27" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>6.22-6.28</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="43" t="n">
         <v>86704</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="43" t="n">
         <v>11722</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="43" t="n">
         <v>17051</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="44" t="n">
         <v>3605</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="45" t="n">
         <v>-7765</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>248</v>
-      </c>
-      <c r="H28" s="15" t="inlineStr">
-        <is>
-          <t>本期改善</t>
+      <c r="G28" s="47" t="n">
+        <v>-0.1012041995287894</v>
+      </c>
+      <c r="H28" s="50" t="n">
+        <v>-1.252702916685956</v>
+      </c>
+      <c r="I28" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>6.29-7.5</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="43" t="n">
         <v>93257</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="43" t="n">
         <v>12985</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="43" t="n">
         <v>17357</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="44" t="n">
         <v>1951</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="45" t="n">
         <v>-5229</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>2536</v>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
-        <is>
-          <t>本期改善</t>
+      <c r="G29" s="47" t="n">
+        <v>-0.06336444645010539</v>
+      </c>
+      <c r="H29" s="48" t="n">
+        <v>3.783975307868404</v>
+      </c>
+      <c r="I29" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>7.6-7.12</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="43" t="n">
         <v>120624</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="43" t="n">
         <v>16854</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="43" t="n">
         <v>20167</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="44" t="n">
         <v>2054</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="45" t="n">
         <v>-4109</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>1120</v>
-      </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>本期改善</t>
+      <c r="G30" s="47" t="n">
+        <v>-0.03849325990755385</v>
+      </c>
+      <c r="H30" s="48" t="n">
+        <v>2.487118654255154</v>
+      </c>
+      <c r="I30" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>7.13-7.19</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="43" t="n">
         <v>100698</v>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="43" t="n">
         <v>13663</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="43" t="n">
         <v>17570</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="44" t="n">
         <v>2405</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="45" t="n">
         <v>-5181</v>
       </c>
-      <c r="G31" s="14" t="n">
-        <v>-1072</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>推广前利润下降</t>
+      <c r="G31" s="47" t="n">
+        <v>-0.0581442482159776</v>
+      </c>
+      <c r="H31" s="50" t="n">
+        <v>-1.965098830842375</v>
+      </c>
+      <c r="I31" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>7.20-7.26</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="43" t="n">
         <v>98448</v>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="43" t="n">
         <v>13513</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="43" t="n">
         <v>18177</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="44" t="n">
         <v>2097</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="45" t="n">
         <v>-5614</v>
       </c>
-      <c r="G32" s="14" t="n">
-        <v>-432</v>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>推广费上升</t>
+      <c r="G32" s="47" t="n">
+        <v>-0.06443338215295813</v>
+      </c>
+      <c r="H32" s="50" t="n">
+        <v>-0.628913393698053</v>
+      </c>
+      <c r="I32" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>7.27-8.2</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="43" t="n">
         <v>107468</v>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="43" t="n">
         <v>15014</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="43" t="n">
         <v>19204</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="44" t="n">
         <v>2127</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="45" t="n">
         <v>-5110</v>
       </c>
-      <c r="G33" s="12" t="n">
-        <v>504</v>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>本期改善</t>
+      <c r="G33" s="47" t="n">
+        <v>-0.05372983428884518</v>
+      </c>
+      <c r="H33" s="48" t="n">
+        <v>1.070354786411295</v>
+      </c>
+      <c r="I33" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1539,1320 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="inlineStr">
+        <is>
+          <t>周报其他费用</t>
+        </is>
+      </c>
+      <c r="C1" s="40" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C2" s="36" t="inlineStr">
+        <is>
+          <t>数据源1「其他费用」= 本表费用 × 当周件数占比（已写入数值，避免打开为0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>5.25-5.31</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C3" s="36" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>6.15-6.21</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C4" s="36" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>6.22-6.28</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C5" s="36" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>6.29-7.5</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>1951</v>
+      </c>
+      <c r="C6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>2054</v>
+      </c>
+      <c r="C7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>7.13-7.19</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>2405</v>
+      </c>
+      <c r="C8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>2097</v>
+      </c>
+      <c r="C9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>2127</v>
+      </c>
+      <c r="C10" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>从推广后利率看变化（去税口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>推广后利率=推广后利润/去税金额；变化单位为百分点(pp)。利率主因：推广前利率下降 vs 推广费率上升。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>一、利率结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>全期推广后利率均为负；最好周 7.6-7.12（-3.85%），最差周 6.22-6.28（-10.12%）。</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>7.6→7.13：推广后利率继续走弱，主因是推广前利率随量/结构下滑（不是费率突然飙升）。</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>7.13→7.20：推广后利率再降，主因是推广费率上升（次链/30包加投）。</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>看利率比只看绝对利润额，更能区分“盘子变小”和“单位赚钱能力变差”。</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>二、周度推广后利率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>成交金额</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>推广前利润</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>推广花费</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>推广前利率</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>推广费率</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>推广后利率</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>后利率环比(pp)</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>利率主因</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>118254</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>15585</v>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>22200</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>-7161</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>0.1489260843071093</v>
+      </c>
+      <c r="G12" s="37" t="n">
+        <v>0.187729716766371</v>
+      </c>
+      <c r="H12" s="47" t="n">
+        <v>-0.06842813955143394</v>
+      </c>
+      <c r="I12" s="42" t="n"/>
+      <c r="J12" s="42" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>5.25-5.31</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>123377</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>16531</v>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>22867</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>-6845</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>0.151404342078056</v>
+      </c>
+      <c r="G13" s="37" t="n">
+        <v>0.1853436547628399</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <v>-0.06269098181676941</v>
+      </c>
+      <c r="I13" s="54" t="n">
+        <v>0.5737157734664531</v>
+      </c>
+      <c r="J13" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>6.15-6.21</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>102108</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>13774</v>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>19490</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>-8013</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>0.1524385518118944</v>
+      </c>
+      <c r="G14" s="37" t="n">
+        <v>0.1908735019376091</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>-0.08867717036192986</v>
+      </c>
+      <c r="I14" s="55" t="n">
+        <v>-2.598618854516045</v>
+      </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>6.22-6.28</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>86704</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>11722</v>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>17051</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>-7765</v>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>0.1527645549163719</v>
+      </c>
+      <c r="G15" s="37" t="n">
+        <v>0.1966581157491693</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>-0.1012041995287894</v>
+      </c>
+      <c r="I15" s="55" t="n">
+        <v>-1.252702916685956</v>
+      </c>
+      <c r="J15" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>6.29-7.5</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>93257</v>
+      </c>
+      <c r="C16" s="43" t="n">
+        <v>12985</v>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>17357</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>-5229</v>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>0.1573428821643038</v>
+      </c>
+      <c r="G16" s="37" t="n">
+        <v>0.186114543058043</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <v>-0.06336444645010539</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>3.783975307868404</v>
+      </c>
+      <c r="J16" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="n">
+        <v>120624</v>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>16854</v>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>20167</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>0.1578872062237625</v>
+      </c>
+      <c r="G17" s="37" t="n">
+        <v>0.1671872010755382</v>
+      </c>
+      <c r="H17" s="47" t="n">
+        <v>-0.03849325990755385</v>
+      </c>
+      <c r="I17" s="54" t="n">
+        <v>2.487118654255154</v>
+      </c>
+      <c r="J17" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>7.13-7.19</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="n">
+        <v>100698</v>
+      </c>
+      <c r="C18" s="43" t="n">
+        <v>13663</v>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>17570</v>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>-5181</v>
+      </c>
+      <c r="F18" s="37" t="n">
+        <v>0.1533258881032721</v>
+      </c>
+      <c r="G18" s="37" t="n">
+        <v>0.1744869288902661</v>
+      </c>
+      <c r="H18" s="47" t="n">
+        <v>-0.0581442482159776</v>
+      </c>
+      <c r="I18" s="55" t="n">
+        <v>-1.965098830842375</v>
+      </c>
+      <c r="J18" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="n">
+        <v>98448</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>13513</v>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>18177</v>
+      </c>
+      <c r="E19" s="45" t="n">
+        <v>-5614</v>
+      </c>
+      <c r="F19" s="37" t="n">
+        <v>0.1551070506585943</v>
+      </c>
+      <c r="G19" s="37" t="n">
+        <v>0.1846400520070178</v>
+      </c>
+      <c r="H19" s="47" t="n">
+        <v>-0.06443338215295813</v>
+      </c>
+      <c r="I19" s="55" t="n">
+        <v>-0.628913393698053</v>
+      </c>
+      <c r="J19" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n">
+        <v>107468</v>
+      </c>
+      <c r="C20" s="43" t="n">
+        <v>15014</v>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>19204</v>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>-5110</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <v>0.1578692004645855</v>
+      </c>
+      <c r="G20" s="37" t="n">
+        <v>0.178699129254325</v>
+      </c>
+      <c r="H20" s="47" t="n">
+        <v>-0.05372983428884518</v>
+      </c>
+      <c r="I20" s="54" t="n">
+        <v>1.070354786411295</v>
+      </c>
+      <c r="J20" s="49" t="inlineStr">
+        <is>
+          <t>利率改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>三、利率恶化ID（成交≥500）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>7.6-7.12 → 7.13-7.19 推广后利率恶化TOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>前周利率</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>后周利率</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>利率变化(pp)</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>前利率变化(pp)</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>费率变化(pp)</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>1059563993918</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="n">
+        <v>-0.1439089011267891</v>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>-0.240581019068933</v>
+      </c>
+      <c r="F36" s="57" t="n">
+        <v>-9.667211794214387</v>
+      </c>
+      <c r="G36" s="55" t="n">
+        <v>-12.89550620759385</v>
+      </c>
+      <c r="H36" s="55" t="n">
+        <v>-4.530836941444971</v>
+      </c>
+      <c r="I36" s="58" t="inlineStr">
+        <is>
+          <t>推广前利率下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>766165464414</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="D37" s="37" t="n">
+        <v>0.1129319305842243</v>
+      </c>
+      <c r="E37" s="37" t="n">
+        <v>0.02294536484640225</v>
+      </c>
+      <c r="F37" s="57" t="n">
+        <v>-8.998656573782204</v>
+      </c>
+      <c r="G37" s="55" t="n">
+        <v>-5.308775377079514</v>
+      </c>
+      <c r="H37" s="54" t="n">
+        <v>2.813813258549341</v>
+      </c>
+      <c r="I37" s="58" t="inlineStr">
+        <is>
+          <t>推广前利率下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>1013887677295</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>混搭5杯</t>
+        </is>
+      </c>
+      <c r="D38" s="47" t="n">
+        <v>-0.08700835869348855</v>
+      </c>
+      <c r="E38" s="47" t="n">
+        <v>-0.155779141629914</v>
+      </c>
+      <c r="F38" s="57" t="n">
+        <v>-6.877078293642544</v>
+      </c>
+      <c r="G38" s="55" t="n">
+        <v>-1.776171672102336</v>
+      </c>
+      <c r="H38" s="54" t="n">
+        <v>4.117649574802437</v>
+      </c>
+      <c r="I38" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>744317232690</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>多规格</t>
+        </is>
+      </c>
+      <c r="D39" s="37" t="n">
+        <v>0.0158180650474342</v>
+      </c>
+      <c r="E39" s="47" t="n">
+        <v>-0.02496143692474282</v>
+      </c>
+      <c r="F39" s="57" t="n">
+        <v>-4.077950197217702</v>
+      </c>
+      <c r="G39" s="55" t="n">
+        <v>-3.923840840142787</v>
+      </c>
+      <c r="H39" s="55" t="n">
+        <v>-1.016733324171709</v>
+      </c>
+      <c r="I39" s="58" t="inlineStr">
+        <is>
+          <t>推广前利率下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>648600900806</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="D40" s="37" t="n">
+        <v>0.004651697839297434</v>
+      </c>
+      <c r="E40" s="47" t="n">
+        <v>-0.03343882234929348</v>
+      </c>
+      <c r="F40" s="57" t="n">
+        <v>-3.809052018859092</v>
+      </c>
+      <c r="G40" s="55" t="n">
+        <v>-0.02764712272561032</v>
+      </c>
+      <c r="H40" s="54" t="n">
+        <v>3.296376008164454</v>
+      </c>
+      <c r="I40" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>648598580775</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>15包</t>
+        </is>
+      </c>
+      <c r="D41" s="37" t="n">
+        <v>0.02017479683727668</v>
+      </c>
+      <c r="E41" s="47" t="n">
+        <v>-0.01606370011603404</v>
+      </c>
+      <c r="F41" s="57" t="n">
+        <v>-3.623849695331072</v>
+      </c>
+      <c r="G41" s="55" t="n">
+        <v>-0.9725483975998761</v>
+      </c>
+      <c r="H41" s="54" t="n">
+        <v>2.007770370316786</v>
+      </c>
+      <c r="I41" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>668566625747</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>袋面主链接</t>
+        </is>
+      </c>
+      <c r="D42" s="47" t="n">
+        <v>-0.02562644800869243</v>
+      </c>
+      <c r="E42" s="47" t="n">
+        <v>-0.04820767862403652</v>
+      </c>
+      <c r="F42" s="57" t="n">
+        <v>-2.258123061534409</v>
+      </c>
+      <c r="G42" s="55" t="n">
+        <v>-0.5108359350044861</v>
+      </c>
+      <c r="H42" s="54" t="n">
+        <v>0.9215804804733108</v>
+      </c>
+      <c r="I42" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>649014937782</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>24包</t>
+        </is>
+      </c>
+      <c r="D43" s="47" t="n">
+        <v>-0.001195647847131685</v>
+      </c>
+      <c r="E43" s="47" t="n">
+        <v>-0.01608904277502523</v>
+      </c>
+      <c r="F43" s="57" t="n">
+        <v>-1.489339492789354</v>
+      </c>
+      <c r="G43" s="55" t="n">
+        <v>-1.405340558390913</v>
+      </c>
+      <c r="H43" s="55" t="n">
+        <v>-0.2441573956604159</v>
+      </c>
+      <c r="I43" s="58" t="inlineStr">
+        <is>
+          <t>推广前利率下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>7.13-7.19 → 7.20-7.26 推广后利率恶化TOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>前周利率</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>后周利率</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>利率变化(pp)</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>前利率变化(pp)</t>
+        </is>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>费率变化(pp)</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="42" t="inlineStr">
+        <is>
+          <t>1013887677295</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>混搭5杯</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="n">
+        <v>-0.155779141629914</v>
+      </c>
+      <c r="E48" s="47" t="n">
+        <v>-0.2412133549273392</v>
+      </c>
+      <c r="F48" s="57" t="n">
+        <v>-8.543421329742523</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>3.389461933117388</v>
+      </c>
+      <c r="H48" s="54" t="n">
+        <v>11.79747336863927</v>
+      </c>
+      <c r="I48" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="42" t="inlineStr">
+        <is>
+          <t>735014804839</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>24/30包</t>
+        </is>
+      </c>
+      <c r="D49" s="37" t="n">
+        <v>0.04788331251076935</v>
+      </c>
+      <c r="E49" s="47" t="n">
+        <v>-0.02474723208431365</v>
+      </c>
+      <c r="F49" s="57" t="n">
+        <v>-7.2630544595083</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>0.3608727360772973</v>
+      </c>
+      <c r="H49" s="54" t="n">
+        <v>7.270850190404602</v>
+      </c>
+      <c r="I49" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="42" t="inlineStr">
+        <is>
+          <t>648600900806</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="n">
+        <v>-0.03343882234929348</v>
+      </c>
+      <c r="E50" s="47" t="n">
+        <v>-0.07705357690498937</v>
+      </c>
+      <c r="F50" s="57" t="n">
+        <v>-4.361475455569589</v>
+      </c>
+      <c r="G50" s="54" t="n">
+        <v>0.8601052598651321</v>
+      </c>
+      <c r="H50" s="54" t="n">
+        <v>5.017566882339469</v>
+      </c>
+      <c r="I50" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" s="42" t="inlineStr">
+        <is>
+          <t>649014937782</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>24包</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="n">
+        <v>-0.01608904277502523</v>
+      </c>
+      <c r="E51" s="47" t="n">
+        <v>-0.05737977034412227</v>
+      </c>
+      <c r="F51" s="57" t="n">
+        <v>-4.129072756909705</v>
+      </c>
+      <c r="G51" s="54" t="n">
+        <v>0.7423445772254345</v>
+      </c>
+      <c r="H51" s="54" t="n">
+        <v>4.728619207095686</v>
+      </c>
+      <c r="I51" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t>648598580775</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>15包</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="n">
+        <v>-0.01606370011603404</v>
+      </c>
+      <c r="E52" s="47" t="n">
+        <v>-0.04329721663149533</v>
+      </c>
+      <c r="F52" s="57" t="n">
+        <v>-2.723351651546129</v>
+      </c>
+      <c r="G52" s="55" t="n">
+        <v>-0.1980292345094808</v>
+      </c>
+      <c r="H52" s="54" t="n">
+        <v>2.602277021626578</v>
+      </c>
+      <c r="I52" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>929504658691</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>日式袋面</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="n">
+        <v>-0.08452206363901109</v>
+      </c>
+      <c r="E53" s="47" t="n">
+        <v>-0.09804489560380623</v>
+      </c>
+      <c r="F53" s="57" t="n">
+        <v>-1.352283196479515</v>
+      </c>
+      <c r="G53" s="55" t="n">
+        <v>-5.226479942143911</v>
+      </c>
+      <c r="H53" s="55" t="n">
+        <v>-3.65680162686493</v>
+      </c>
+      <c r="I53" s="58" t="inlineStr">
+        <is>
+          <t>推广前利率下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>649361890551</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>袋面次链接</t>
+        </is>
+      </c>
+      <c r="D54" s="47" t="n">
+        <v>-0.1144269475234252</v>
+      </c>
+      <c r="E54" s="47" t="n">
+        <v>-0.1237914008246476</v>
+      </c>
+      <c r="F54" s="57" t="n">
+        <v>-0.9364453301222389</v>
+      </c>
+      <c r="G54" s="54" t="n">
+        <v>0.5268246301027721</v>
+      </c>
+      <c r="H54" s="54" t="n">
+        <v>1.922812385227718</v>
+      </c>
+      <c r="I54" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>649735171438</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>杯面主链接</t>
+        </is>
+      </c>
+      <c r="D55" s="47" t="n">
+        <v>-0.07926454209456806</v>
+      </c>
+      <c r="E55" s="47" t="n">
+        <v>-0.08469679779072363</v>
+      </c>
+      <c r="F55" s="57" t="n">
+        <v>-0.5432255696155575</v>
+      </c>
+      <c r="G55" s="55" t="n">
+        <v>-0.3828713230439471</v>
+      </c>
+      <c r="H55" s="54" t="n">
+        <v>0.4193783018812902</v>
+      </c>
+      <c r="I55" s="51" t="inlineStr">
+        <is>
+          <t>推广费率上升</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A34:I34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1845,14 +3349,14 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2749,7 +4253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3494,13 +4998,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3545,6 +5049,20 @@
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>本报告用于领导决策；明细见天猫利润分析.xlsx；搭配桥接见利润变化_规格搭配关系.xlsx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>推广后利率=推广后利润/去税金额；利率环比以百分点(pp)表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>利率主因判定：后利率走弱时，若推广前利率下降幅度 ≥ 推广费率上升幅度，则判为「推广前利率下降」；反之判为「推广费率上升」。</t>
         </is>
       </c>
     </row>
@@ -3560,7 +5078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5847,7 +7365,2385 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>全量商品ID · 每周推广后利率明细表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>推广后利率=推广后/去税金额；变化列为百分点(pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>5.25-5.31</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>6.15-6.21</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>6.22-6.28</t>
+        </is>
+      </c>
+      <c r="H4" s="26" t="inlineStr">
+        <is>
+          <t>6.29-7.5</t>
+        </is>
+      </c>
+      <c r="I4" s="26" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="J4" s="26" t="inlineStr">
+        <is>
+          <t>7.13-7.19</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t>7.6→7.13利率变化(pp)</t>
+        </is>
+      </c>
+      <c r="N4" s="26" t="inlineStr">
+        <is>
+          <t>7.13→7.20利率变化(pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>916072786304</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>小规格</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>营多印尼进口营多捞面方便面火鸡面干拌面10包宿舍速食泡面夜宵</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="n">
+        <v>-0.2292280035686974</v>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>-0.01066181524482585</v>
+      </c>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="47" t="n">
+        <v>-0.1415258015463917</v>
+      </c>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="47" t="n">
+        <v>-0.005390827077747989</v>
+      </c>
+      <c r="J5" s="47" t="n">
+        <v>-0.3239972269197584</v>
+      </c>
+      <c r="K5" s="37" t="n"/>
+      <c r="L5" s="47" t="n">
+        <v>-0.09025823712486104</v>
+      </c>
+      <c r="M5" s="57" t="n">
+        <v>-31.86063998420104</v>
+      </c>
+      <c r="N5" s="60" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>898120785283</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>韩式袋面</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>营多韩式火鸡面袋装拌面干拌面泡面方便面速食面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0.02654954633204633</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>-0.1731839615728329</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <v>0.05819902465753424</v>
+      </c>
+      <c r="G6" s="47" t="n">
+        <v>-0.0018879852003062</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>-0.1015672374815906</v>
+      </c>
+      <c r="I6" s="47" t="n">
+        <v>-0.1375562469040248</v>
+      </c>
+      <c r="J6" s="47" t="n">
+        <v>-0.3704171804635761</v>
+      </c>
+      <c r="K6" s="37" t="n"/>
+      <c r="L6" s="37" t="n">
+        <v>0.1338752932380428</v>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>-23.28609335595514</v>
+      </c>
+      <c r="N6" s="60" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>947413291596</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>杯面</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面杯装方便面泡面速食干拌面原味整箱批发印尼进口桶装拌面</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="n">
+        <v>-0.0005978038077969174</v>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>-0.1159487274315667</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <v>-0.1174507486238532</v>
+      </c>
+      <c r="G7" s="47" t="n">
+        <v>-0.0253509481017983</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>-0.09308207154811714</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>-0.1881286311368303</v>
+      </c>
+      <c r="J7" s="47" t="n">
+        <v>-0.4180311218348624</v>
+      </c>
+      <c r="K7" s="37" t="n"/>
+      <c r="L7" s="47" t="n">
+        <v>-0.008211340163191295</v>
+      </c>
+      <c r="M7" s="57" t="n">
+        <v>-22.99024906980321</v>
+      </c>
+      <c r="N7" s="60" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>648604228786</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>INDOMIE营多日式杯面原味经典泡面整箱批发速食宿舍旅行宵夜宿舍</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="n">
+        <v>-0.1222392746405501</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.03874047952023987</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>0.03178109977467327</v>
+      </c>
+      <c r="G8" s="47" t="n">
+        <v>-0.04138010399714721</v>
+      </c>
+      <c r="H8" s="37" t="n">
+        <v>0.03279836781504986</v>
+      </c>
+      <c r="I8" s="37" t="n">
+        <v>0.05727410156225831</v>
+      </c>
+      <c r="J8" s="47" t="n">
+        <v>-0.1652379474677259</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <v>0.04846366836014676</v>
+      </c>
+      <c r="L8" s="37" t="n">
+        <v>0.03828812617279125</v>
+      </c>
+      <c r="M8" s="57" t="n">
+        <v>-22.25120490299842</v>
+      </c>
+      <c r="N8" s="60" t="n">
+        <v>21.37016158278727</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>932687928859</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>8包组合</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面八口味袋装泡面拌面速食面干拌面方便面宿舍宵夜速食家用</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>0.2585031627174813</v>
+      </c>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n">
+        <v>0.1266820208333333</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <v>0.09051349729180772</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>0.03994734900815627</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>0.09535997596429709</v>
+      </c>
+      <c r="J9" s="47" t="n">
+        <v>-0.02097454663740398</v>
+      </c>
+      <c r="K9" s="37" t="n">
+        <v>0.01592189646996839</v>
+      </c>
+      <c r="L9" s="37" t="n">
+        <v>0.1291612200392927</v>
+      </c>
+      <c r="M9" s="57" t="n">
+        <v>-11.63345226017011</v>
+      </c>
+      <c r="N9" s="60" t="n">
+        <v>3.689644310737236</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>1028450344901</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>韩式火鸡</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>营多韩式火鸡面袋装拌面干拌面泡面方便面速食面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n">
+        <v>0.01159855013970816</v>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>0.02084896291504959</v>
+      </c>
+      <c r="G10" s="47" t="n">
+        <v>-0.1734958255849286</v>
+      </c>
+      <c r="H10" s="47" t="n">
+        <v>-0.5193426055276382</v>
+      </c>
+      <c r="I10" s="37" t="n">
+        <v>0.0006451935483870968</v>
+      </c>
+      <c r="J10" s="47" t="n">
+        <v>-0.1048163553203998</v>
+      </c>
+      <c r="K10" s="37" t="n"/>
+      <c r="L10" s="37" t="n">
+        <v>0.01063182270896768</v>
+      </c>
+      <c r="M10" s="57" t="n">
+        <v>-10.54615488687869</v>
+      </c>
+      <c r="N10" s="60" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>1059563993918</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>营多进口新口味巴东炖牛肉味捞面印尼料理方便面泡面捞面夜宵速食</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="47" t="n">
+        <v>-0.2496101512725598</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <v>-0.3759256847812077</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <v>-0.1439089011267891</v>
+      </c>
+      <c r="J11" s="47" t="n">
+        <v>-0.240581019068933</v>
+      </c>
+      <c r="K11" s="47" t="n">
+        <v>-0.1270414163782696</v>
+      </c>
+      <c r="L11" s="47" t="n">
+        <v>-0.1167775493603669</v>
+      </c>
+      <c r="M11" s="57" t="n">
+        <v>-9.667211794214387</v>
+      </c>
+      <c r="N11" s="60" t="n">
+        <v>11.35396026906634</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>649729851594</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>小规格</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面袋装8包装泡面宿舍速食面热干面干拌面方便面火鸡面食品</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>-0.0436315215308308</v>
+      </c>
+      <c r="E12" s="37" t="n">
+        <v>0.08025506046685341</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>0.0343307461626575</v>
+      </c>
+      <c r="G12" s="47" t="n">
+        <v>-0.03691385554561717</v>
+      </c>
+      <c r="H12" s="37" t="n"/>
+      <c r="I12" s="37" t="n">
+        <v>0.06648278908668731</v>
+      </c>
+      <c r="J12" s="47" t="n">
+        <v>-0.02601563466625175</v>
+      </c>
+      <c r="K12" s="37" t="n"/>
+      <c r="L12" s="37" t="n">
+        <v>0.1343134976525822</v>
+      </c>
+      <c r="M12" s="57" t="n">
+        <v>-9.249842375293907</v>
+      </c>
+      <c r="N12" s="60" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>766165464414</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>营多进口新口味巴东炖牛肉味捞面印尼料理方便面泡面捞面夜宵速食</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>0.02395030199039438</v>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>0.07102430000621136</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>0.05327694922430919</v>
+      </c>
+      <c r="G13" s="37" t="n">
+        <v>0.04945717606886779</v>
+      </c>
+      <c r="H13" s="37" t="n">
+        <v>0.07723261483039705</v>
+      </c>
+      <c r="I13" s="37" t="n">
+        <v>0.1129319305842243</v>
+      </c>
+      <c r="J13" s="37" t="n">
+        <v>0.02294536484640225</v>
+      </c>
+      <c r="K13" s="37" t="n">
+        <v>0.08623114392634937</v>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>0.1009672900151448</v>
+      </c>
+      <c r="M13" s="57" t="n">
+        <v>-8.998656573782204</v>
+      </c>
+      <c r="N13" s="60" t="n">
+        <v>6.328577907994712</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>969433743398</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>韩蘑菇</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>新品营多捞面韩式辣蘑菇汤面泡面方便面速食干拌面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="n">
+        <v>-0.1941551607070788</v>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>-0.371074765596512</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>0.02454920292787431</v>
+      </c>
+      <c r="G14" s="47" t="n">
+        <v>-0.2935445844793713</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>-0.1570344125608272</v>
+      </c>
+      <c r="I14" s="37" t="n">
+        <v>0.003126659843342036</v>
+      </c>
+      <c r="J14" s="47" t="n">
+        <v>-0.06762602934961258</v>
+      </c>
+      <c r="K14" s="37" t="n">
+        <v>0.02888850870541982</v>
+      </c>
+      <c r="L14" s="37" t="n">
+        <v>0.05987968235808497</v>
+      </c>
+      <c r="M14" s="57" t="n">
+        <v>-7.075268919295461</v>
+      </c>
+      <c r="N14" s="60" t="n">
+        <v>9.651453805503241</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>1013887677295</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>混搭5杯</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>进口营多原味杯面日式杯面韩式杯面泡面方便面汤面宿舍速食夜宵</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="n">
+        <v>-0.1366870079600083</v>
+      </c>
+      <c r="E15" s="47" t="n">
+        <v>-0.2789896744570154</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <v>-0.1395971292505579</v>
+      </c>
+      <c r="G15" s="47" t="n">
+        <v>-0.2326971545122294</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>-0.07174213266428538</v>
+      </c>
+      <c r="I15" s="47" t="n">
+        <v>-0.08700835869348855</v>
+      </c>
+      <c r="J15" s="47" t="n">
+        <v>-0.155779141629914</v>
+      </c>
+      <c r="K15" s="47" t="n">
+        <v>-0.2412133549273392</v>
+      </c>
+      <c r="L15" s="47" t="n">
+        <v>-0.1142520035671411</v>
+      </c>
+      <c r="M15" s="57" t="n">
+        <v>-6.877078293642544</v>
+      </c>
+      <c r="N15" s="57" t="n">
+        <v>-8.543421329742523</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>976479938842</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>【U选】原味5</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>【天猫U选】indomie营多大骨牛肉味捞面拌面5包</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="n">
+        <v>-0.7526177761173377</v>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>-0.4837890169740151</v>
+      </c>
+      <c r="F16" s="47" t="n">
+        <v>-0.541417128208469</v>
+      </c>
+      <c r="G16" s="47" t="n">
+        <v>-0.5257722782828282</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <v>-0.5284647943676938</v>
+      </c>
+      <c r="I16" s="47" t="n">
+        <v>-0.485249322152341</v>
+      </c>
+      <c r="J16" s="47" t="n">
+        <v>-0.5364933302869287</v>
+      </c>
+      <c r="K16" s="47" t="n">
+        <v>-0.5315667079365078</v>
+      </c>
+      <c r="L16" s="47" t="n">
+        <v>-0.4952028791553418</v>
+      </c>
+      <c r="M16" s="57" t="n">
+        <v>-5.124400813458774</v>
+      </c>
+      <c r="N16" s="60" t="n">
+        <v>0.4926622350420851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>744317232690</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>多规格</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面汤面清香牛肉味方便面泡面速食食品泡面拉面整箱旅行宿舍</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="n">
+        <v>-0.1074006326162462</v>
+      </c>
+      <c r="E17" s="47" t="n">
+        <v>-0.01717817483586653</v>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>0.06238457087458149</v>
+      </c>
+      <c r="G17" s="47" t="n">
+        <v>-0.04237377793097505</v>
+      </c>
+      <c r="H17" s="47" t="n">
+        <v>-0.1477115483159067</v>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>0.0158180650474342</v>
+      </c>
+      <c r="J17" s="47" t="n">
+        <v>-0.02496143692474282</v>
+      </c>
+      <c r="K17" s="37" t="n">
+        <v>0.0243564740861825</v>
+      </c>
+      <c r="L17" s="47" t="n">
+        <v>-0.1333064124347133</v>
+      </c>
+      <c r="M17" s="57" t="n">
+        <v>-4.077950197217702</v>
+      </c>
+      <c r="N17" s="60" t="n">
+        <v>4.931791101092532</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>775016827115</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>进口营多原味杯面日式杯面韩式杯面泡面方便面汤面宿舍速食夜宵</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n">
+        <v>0.03537224375829213</v>
+      </c>
+      <c r="F18" s="47" t="n">
+        <v>-0.03699988566308244</v>
+      </c>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="37" t="n">
+        <v>0.0799147269265639</v>
+      </c>
+      <c r="I18" s="37" t="n">
+        <v>0.07214693584229391</v>
+      </c>
+      <c r="J18" s="37" t="n">
+        <v>0.03227420549797205</v>
+      </c>
+      <c r="K18" s="37" t="n"/>
+      <c r="L18" s="37" t="n"/>
+      <c r="M18" s="57" t="n">
+        <v>-3.987273034432186</v>
+      </c>
+      <c r="N18" s="60" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>648600900806</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="n">
+        <v>-0.002558109316522905</v>
+      </c>
+      <c r="E19" s="47" t="n">
+        <v>-0.008452087804336912</v>
+      </c>
+      <c r="F19" s="47" t="n">
+        <v>-0.02816518563284378</v>
+      </c>
+      <c r="G19" s="47" t="n">
+        <v>-0.04264715764716478</v>
+      </c>
+      <c r="H19" s="47" t="n">
+        <v>-0.02568138151714817</v>
+      </c>
+      <c r="I19" s="37" t="n">
+        <v>0.004651697839297434</v>
+      </c>
+      <c r="J19" s="47" t="n">
+        <v>-0.03343882234929348</v>
+      </c>
+      <c r="K19" s="47" t="n">
+        <v>-0.07705357690498937</v>
+      </c>
+      <c r="L19" s="47" t="n">
+        <v>-0.05299056122910207</v>
+      </c>
+      <c r="M19" s="57" t="n">
+        <v>-3.809052018859092</v>
+      </c>
+      <c r="N19" s="57" t="n">
+        <v>-4.361475455569589</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>648598580775</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>15包</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>进口营多捞面15包Indomie方便面干拌面夜宵方便速食五连包85g*5</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="n">
+        <v>-0.001268674494829481</v>
+      </c>
+      <c r="E20" s="47" t="n">
+        <v>-0.01780476608738745</v>
+      </c>
+      <c r="F20" s="47" t="n">
+        <v>-0.03337757803198677</v>
+      </c>
+      <c r="G20" s="47" t="n">
+        <v>-0.05872249523911046</v>
+      </c>
+      <c r="H20" s="47" t="n">
+        <v>-0.05219190944742513</v>
+      </c>
+      <c r="I20" s="37" t="n">
+        <v>0.02017479683727668</v>
+      </c>
+      <c r="J20" s="47" t="n">
+        <v>-0.01606370011603404</v>
+      </c>
+      <c r="K20" s="47" t="n">
+        <v>-0.04329721663149533</v>
+      </c>
+      <c r="L20" s="47" t="n">
+        <v>-0.04341956561307014</v>
+      </c>
+      <c r="M20" s="57" t="n">
+        <v>-3.623849695331072</v>
+      </c>
+      <c r="N20" s="57" t="n">
+        <v>-2.723351651546129</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>969423151512</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>日韩混搭</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面甜辣炸鸡火鸡面辣蘑菇泡面方便面速食干拌面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="n">
+        <v>-0.09007123489469443</v>
+      </c>
+      <c r="E21" s="47" t="n">
+        <v>-0.05099129117218405</v>
+      </c>
+      <c r="F21" s="47" t="n">
+        <v>-0.2417514411638328</v>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>-0.2115805698130154</v>
+      </c>
+      <c r="H21" s="47" t="n">
+        <v>-0.4168066658684759</v>
+      </c>
+      <c r="I21" s="47" t="n">
+        <v>-0.05449272659768715</v>
+      </c>
+      <c r="J21" s="47" t="n">
+        <v>-0.07953483012680367</v>
+      </c>
+      <c r="K21" s="47" t="n">
+        <v>-0.002987339211059291</v>
+      </c>
+      <c r="L21" s="47" t="n">
+        <v>-0.1345376314192298</v>
+      </c>
+      <c r="M21" s="57" t="n">
+        <v>-2.504210352911652</v>
+      </c>
+      <c r="N21" s="60" t="n">
+        <v>7.654749091574438</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>668566625747</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>袋面主链接</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>印尼营多捞面进口网红泡面袋装方便面速食食品拉面火鸡面拌面整箱</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="n">
+        <v>-0.05808137419157384</v>
+      </c>
+      <c r="E22" s="47" t="n">
+        <v>-0.05502350578225519</v>
+      </c>
+      <c r="F22" s="47" t="n">
+        <v>-0.05105262140555219</v>
+      </c>
+      <c r="G22" s="47" t="n">
+        <v>-0.08102095039668043</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>-0.04443874486902612</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>-0.02562644800869243</v>
+      </c>
+      <c r="J22" s="47" t="n">
+        <v>-0.04820767862403652</v>
+      </c>
+      <c r="K22" s="47" t="n">
+        <v>-0.04588338217443783</v>
+      </c>
+      <c r="L22" s="47" t="n">
+        <v>-0.01854118328258559</v>
+      </c>
+      <c r="M22" s="57" t="n">
+        <v>-2.258123061534409</v>
+      </c>
+      <c r="N22" s="60" t="n">
+        <v>0.2324296449598695</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>649014937782</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>24包</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>印尼营多捞面干拌面一整箱24袋装批发泡面宿舍速食方便面火鸡面</t>
+        </is>
+      </c>
+      <c r="D23" s="47" t="n">
+        <v>-0.01747225728146963</v>
+      </c>
+      <c r="E23" s="47" t="n">
+        <v>-0.02298666267427357</v>
+      </c>
+      <c r="F23" s="47" t="n">
+        <v>-0.01695157342113822</v>
+      </c>
+      <c r="G23" s="47" t="n">
+        <v>-0.05611041530285661</v>
+      </c>
+      <c r="H23" s="47" t="n">
+        <v>-0.05379273471208387</v>
+      </c>
+      <c r="I23" s="47" t="n">
+        <v>-0.001195647847131685</v>
+      </c>
+      <c r="J23" s="47" t="n">
+        <v>-0.01608904277502523</v>
+      </c>
+      <c r="K23" s="47" t="n">
+        <v>-0.05737977034412227</v>
+      </c>
+      <c r="L23" s="47" t="n">
+        <v>-0.08545505404962028</v>
+      </c>
+      <c r="M23" s="57" t="n">
+        <v>-1.489339492789354</v>
+      </c>
+      <c r="N23" s="57" t="n">
+        <v>-4.129072756909705</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>649731447266</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>20包经典/牛系列</t>
+        </is>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>营多印尼进口营多捞面方便面火鸡面干拌面20包宿舍速食泡面夜宵</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>0.1389044754267977</v>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>-0.1222797776639344</v>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>0.06793984363349269</v>
+      </c>
+      <c r="G24" s="37" t="n">
+        <v>0.1672958585491339</v>
+      </c>
+      <c r="H24" s="37" t="n">
+        <v>0.1329881870699541</v>
+      </c>
+      <c r="I24" s="37" t="n">
+        <v>0.1394936888773926</v>
+      </c>
+      <c r="J24" s="37" t="n">
+        <v>0.1255094390584583</v>
+      </c>
+      <c r="K24" s="37" t="n">
+        <v>0.1590605170431211</v>
+      </c>
+      <c r="L24" s="37" t="n">
+        <v>0.1474807070341139</v>
+      </c>
+      <c r="M24" s="57" t="n">
+        <v>-1.398424981893431</v>
+      </c>
+      <c r="N24" s="60" t="n">
+        <v>3.355107798466281</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>649369494424</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>24包经典/牛系列</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面干拌面一整箱24袋装批发泡面混搭宿舍速食方便面火鸡面</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="n">
+        <v>0.0634271181335149</v>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>0.0348948866353324</v>
+      </c>
+      <c r="F25" s="47" t="n">
+        <v>-0.02473828299894192</v>
+      </c>
+      <c r="G25" s="47" t="n">
+        <v>-0.03507949527024552</v>
+      </c>
+      <c r="H25" s="37" t="n">
+        <v>0.02571352598456883</v>
+      </c>
+      <c r="I25" s="37" t="n">
+        <v>0.06190780304505662</v>
+      </c>
+      <c r="J25" s="37" t="n">
+        <v>0.04842721099260607</v>
+      </c>
+      <c r="K25" s="37" t="n">
+        <v>0.06970374094712377</v>
+      </c>
+      <c r="L25" s="37" t="n">
+        <v>0.03573486960845693</v>
+      </c>
+      <c r="M25" s="57" t="n">
+        <v>-1.348059205245056</v>
+      </c>
+      <c r="N25" s="60" t="n">
+        <v>2.12765299545177</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>898076297965</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>番茄牛肉</t>
+        </is>
+      </c>
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>进口正品意面风味奶香番茄牛肉味意式拌面营多捞面早餐儿童宝妈餐</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="n">
+        <v>-0.349296750538086</v>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>-0.04562394500437502</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>-0.1188903746083469</v>
+      </c>
+      <c r="G26" s="47" t="n">
+        <v>-0.2273868306487202</v>
+      </c>
+      <c r="H26" s="47" t="n">
+        <v>-0.110128974051274</v>
+      </c>
+      <c r="I26" s="47" t="n">
+        <v>-0.09292210550478396</v>
+      </c>
+      <c r="J26" s="47" t="n">
+        <v>-0.1024918646978801</v>
+      </c>
+      <c r="K26" s="47" t="n">
+        <v>-0.1160047907999586</v>
+      </c>
+      <c r="L26" s="47" t="n">
+        <v>-0.1384597982251872</v>
+      </c>
+      <c r="M26" s="57" t="n">
+        <v>-0.9569759193096119</v>
+      </c>
+      <c r="N26" s="57" t="n">
+        <v>-1.351292610207852</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>649361890551</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>袋面次链接</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面印尼进口Indomie网红夜宵早餐方便面火鸡面泡面拌面</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="n">
+        <v>-0.1356870846168906</v>
+      </c>
+      <c r="E27" s="47" t="n">
+        <v>-0.1402044686407309</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <v>-0.1753318261851623</v>
+      </c>
+      <c r="G27" s="47" t="n">
+        <v>-0.1707065471172638</v>
+      </c>
+      <c r="H27" s="47" t="n">
+        <v>-0.1054197823084479</v>
+      </c>
+      <c r="I27" s="47" t="n">
+        <v>-0.1057286534461766</v>
+      </c>
+      <c r="J27" s="47" t="n">
+        <v>-0.1144269475234252</v>
+      </c>
+      <c r="K27" s="47" t="n">
+        <v>-0.1237914008246476</v>
+      </c>
+      <c r="L27" s="47" t="n">
+        <v>-0.125206150418703</v>
+      </c>
+      <c r="M27" s="57" t="n">
+        <v>-0.8698294077248578</v>
+      </c>
+      <c r="N27" s="57" t="n">
+        <v>-0.9364453301222389</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>649735171438</t>
+        </is>
+      </c>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>杯面主链接</t>
+        </is>
+      </c>
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>印尼进口indomie营多捞面杯面速食泡面干拌面盒桶装方便面火鸡面</t>
+        </is>
+      </c>
+      <c r="D28" s="47" t="n">
+        <v>-0.07240274561436029</v>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>-0.07445002490295884</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <v>-0.1417498488080965</v>
+      </c>
+      <c r="G28" s="47" t="n">
+        <v>-0.1322413684665259</v>
+      </c>
+      <c r="H28" s="47" t="n">
+        <v>-0.09015030893918437</v>
+      </c>
+      <c r="I28" s="47" t="n">
+        <v>-0.07169965634685091</v>
+      </c>
+      <c r="J28" s="47" t="n">
+        <v>-0.07926454209456806</v>
+      </c>
+      <c r="K28" s="47" t="n">
+        <v>-0.08469679779072363</v>
+      </c>
+      <c r="L28" s="47" t="n">
+        <v>-0.0580650269661092</v>
+      </c>
+      <c r="M28" s="57" t="n">
+        <v>-0.7564885747717145</v>
+      </c>
+      <c r="N28" s="57" t="n">
+        <v>-0.5432255696155575</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>735014804839</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>24/30包</t>
+        </is>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>进口营多捞面多口味Indomie网红方便面干拌面泡面30包整箱批发面</t>
+        </is>
+      </c>
+      <c r="D29" s="47" t="n">
+        <v>-0.02590640704255268</v>
+      </c>
+      <c r="E29" s="47" t="n">
+        <v>-0.01885560752249972</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>0.07108861924532074</v>
+      </c>
+      <c r="G29" s="47" t="n">
+        <v>-0.0113106122384899</v>
+      </c>
+      <c r="H29" s="37" t="n">
+        <v>0.01542449442898462</v>
+      </c>
+      <c r="I29" s="37" t="n">
+        <v>0.05254502343436088</v>
+      </c>
+      <c r="J29" s="37" t="n">
+        <v>0.04788331251076935</v>
+      </c>
+      <c r="K29" s="47" t="n">
+        <v>-0.02474723208431365</v>
+      </c>
+      <c r="L29" s="47" t="n">
+        <v>-0.01593177775107071</v>
+      </c>
+      <c r="M29" s="57" t="n">
+        <v>-0.4661710923591529</v>
+      </c>
+      <c r="N29" s="57" t="n">
+        <v>-7.2630544595083</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>1060999732877</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>原味大包</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>印尼进口大大包营多原味捞面5包干拌面速食超大包方便面速食宵夜</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="37" t="n">
+        <v>0.09021140108712532</v>
+      </c>
+      <c r="H30" s="47" t="n">
+        <v>-0.0236109640756936</v>
+      </c>
+      <c r="I30" s="47" t="n">
+        <v>-0.02274184998149278</v>
+      </c>
+      <c r="J30" s="47" t="n">
+        <v>-0.02396654248934462</v>
+      </c>
+      <c r="K30" s="47" t="n">
+        <v>-0.0216475419998736</v>
+      </c>
+      <c r="L30" s="47" t="n">
+        <v>-0.03582941704520206</v>
+      </c>
+      <c r="M30" s="57" t="n">
+        <v>-0.1224692507851847</v>
+      </c>
+      <c r="N30" s="60" t="n">
+        <v>0.2319000489471021</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>1057479227624</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
+      <c r="G31" s="47" t="n">
+        <v>-0.2788516171963339</v>
+      </c>
+      <c r="H31" s="47" t="n">
+        <v>-0.2718874197075241</v>
+      </c>
+      <c r="I31" s="47" t="n">
+        <v>-0.3130277372444998</v>
+      </c>
+      <c r="J31" s="47" t="n">
+        <v>-0.3140203069822095</v>
+      </c>
+      <c r="K31" s="47" t="n">
+        <v>-0.2321077519727026</v>
+      </c>
+      <c r="L31" s="47" t="n">
+        <v>-0.2528622648121945</v>
+      </c>
+      <c r="M31" s="57" t="n">
+        <v>-0.09925697377096698</v>
+      </c>
+      <c r="N31" s="60" t="n">
+        <v>8.191255500950687</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>937005385662</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>日式袋面</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>进口营多正品捞面日式鸡肉鸡汤辛辣味袋装泡面辣味速食方便面汤面</t>
+        </is>
+      </c>
+      <c r="D32" s="47" t="n">
+        <v>-0.2984279842162213</v>
+      </c>
+      <c r="E32" s="47" t="n">
+        <v>-0.3181864738660907</v>
+      </c>
+      <c r="F32" s="47" t="n">
+        <v>-0.4503546454945055</v>
+      </c>
+      <c r="G32" s="37" t="n">
+        <v>0.06940142567603046</v>
+      </c>
+      <c r="H32" s="37" t="n">
+        <v>0.01046512156963324</v>
+      </c>
+      <c r="I32" s="47" t="n">
+        <v>-0.07102412302259886</v>
+      </c>
+      <c r="J32" s="47" t="n">
+        <v>-0.0707403204495874</v>
+      </c>
+      <c r="K32" s="47" t="n">
+        <v>-0.1021684906903335</v>
+      </c>
+      <c r="L32" s="47" t="n">
+        <v>-0.3319270274150869</v>
+      </c>
+      <c r="M32" s="60" t="n">
+        <v>0.02838025730114574</v>
+      </c>
+      <c r="N32" s="57" t="n">
+        <v>-3.142817024074608</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>1058280415678</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>原味大包</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>印尼进口大大包营多原味捞面5包干拌面速食超大包方便面速食宵夜</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="37" t="n">
+        <v>0.05565584412593206</v>
+      </c>
+      <c r="H33" s="37" t="n">
+        <v>0.01293273491189149</v>
+      </c>
+      <c r="I33" s="37" t="n">
+        <v>0.01062712596045652</v>
+      </c>
+      <c r="J33" s="37" t="n">
+        <v>0.01747524045269288</v>
+      </c>
+      <c r="K33" s="37" t="n">
+        <v>0.0378605402223795</v>
+      </c>
+      <c r="L33" s="37" t="n">
+        <v>0.02384754179744173</v>
+      </c>
+      <c r="M33" s="60" t="n">
+        <v>0.6848114492236358</v>
+      </c>
+      <c r="N33" s="60" t="n">
+        <v>2.038529976968662</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>929504658691</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>日式袋面</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面日式鸡肉汤面原味辛辣味袋装泡面方便面速食宿舍夜宵食品</t>
+        </is>
+      </c>
+      <c r="D34" s="47" t="n">
+        <v>-0.1155524861891685</v>
+      </c>
+      <c r="E34" s="47" t="n">
+        <v>-0.2162453419754798</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <v>-0.3179050216024152</v>
+      </c>
+      <c r="G34" s="47" t="n">
+        <v>-0.5395753993811226</v>
+      </c>
+      <c r="H34" s="47" t="n">
+        <v>-0.2444998346861985</v>
+      </c>
+      <c r="I34" s="47" t="n">
+        <v>-0.09576864416010152</v>
+      </c>
+      <c r="J34" s="47" t="n">
+        <v>-0.08452206363901109</v>
+      </c>
+      <c r="K34" s="47" t="n">
+        <v>-0.09804489560380623</v>
+      </c>
+      <c r="L34" s="47" t="n">
+        <v>-0.1521974947925559</v>
+      </c>
+      <c r="M34" s="60" t="n">
+        <v>1.124658052109043</v>
+      </c>
+      <c r="N34" s="57" t="n">
+        <v>-1.352283196479515</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>885645733215</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>大骨牛肉</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>进口营多大骨番茄牛肉味营多捞面意式泡面宿舍宿舍宵夜速食方便面</t>
+        </is>
+      </c>
+      <c r="D35" s="47" t="n">
+        <v>-0.1317069145833333</v>
+      </c>
+      <c r="E35" s="37" t="n">
+        <v>0.009694580539976523</v>
+      </c>
+      <c r="F35" s="47" t="n">
+        <v>-0.1468501875304432</v>
+      </c>
+      <c r="G35" s="47" t="n">
+        <v>-0.4397879455758426</v>
+      </c>
+      <c r="H35" s="47" t="n">
+        <v>-0.1317695430107527</v>
+      </c>
+      <c r="I35" s="47" t="n">
+        <v>-0.1167922934746605</v>
+      </c>
+      <c r="J35" s="47" t="n">
+        <v>-0.1042911799817542</v>
+      </c>
+      <c r="K35" s="47" t="n">
+        <v>-0.05014758976052849</v>
+      </c>
+      <c r="L35" s="37" t="n"/>
+      <c r="M35" s="60" t="n">
+        <v>1.250111349290627</v>
+      </c>
+      <c r="N35" s="60" t="n">
+        <v>5.414359022122571</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>1019572719528</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>印尼进口营多捞面杯面原味甜辣蘑菇味整箱速食拌面拉面泡面方便面</t>
+        </is>
+      </c>
+      <c r="D36" s="37" t="n">
+        <v>0.09710096312849162</v>
+      </c>
+      <c r="E36" s="37" t="n"/>
+      <c r="F36" s="37" t="n"/>
+      <c r="G36" s="37" t="n"/>
+      <c r="H36" s="37" t="n">
+        <v>0.05778510352045671</v>
+      </c>
+      <c r="I36" s="37" t="n">
+        <v>0.09524966972477063</v>
+      </c>
+      <c r="J36" s="37" t="n">
+        <v>0.1106041474860335</v>
+      </c>
+      <c r="K36" s="37" t="n"/>
+      <c r="L36" s="37" t="n"/>
+      <c r="M36" s="60" t="n">
+        <v>1.535447776126289</v>
+      </c>
+      <c r="N36" s="60" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>648681860568</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>原味大包</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>indomie印尼进口营多原味大大包129g捞面方便面速食食品宵夜小吃</t>
+        </is>
+      </c>
+      <c r="D37" s="47" t="n">
+        <v>-0.107344303062112</v>
+      </c>
+      <c r="E37" s="47" t="n">
+        <v>-0.08257158927417305</v>
+      </c>
+      <c r="F37" s="47" t="n">
+        <v>-0.1507935402623672</v>
+      </c>
+      <c r="G37" s="47" t="n">
+        <v>-0.08365747216721858</v>
+      </c>
+      <c r="H37" s="37" t="n">
+        <v>0.02734341727984932</v>
+      </c>
+      <c r="I37" s="47" t="n">
+        <v>-0.1502086283650253</v>
+      </c>
+      <c r="J37" s="47" t="n">
+        <v>-0.1340600460745176</v>
+      </c>
+      <c r="K37" s="47" t="n">
+        <v>-0.1065915102410212</v>
+      </c>
+      <c r="L37" s="47" t="n">
+        <v>-0.2774797991172506</v>
+      </c>
+      <c r="M37" s="60" t="n">
+        <v>1.61485822905077</v>
+      </c>
+      <c r="N37" s="60" t="n">
+        <v>2.746853583349641</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>976467954327</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>十全十美</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面多口味袋装泡面拌面速食面干拌面方便面速食宵夜宿舍旅行</t>
+        </is>
+      </c>
+      <c r="D38" s="47" t="n">
+        <v>-0.6418353071852341</v>
+      </c>
+      <c r="E38" s="47" t="n">
+        <v>-0.3536187886792452</v>
+      </c>
+      <c r="F38" s="37" t="n"/>
+      <c r="G38" s="47" t="n">
+        <v>-0.4328253049946864</v>
+      </c>
+      <c r="H38" s="47" t="n">
+        <v>-0.3721913857296136</v>
+      </c>
+      <c r="I38" s="47" t="n">
+        <v>-0.3361760807651434</v>
+      </c>
+      <c r="J38" s="47" t="n">
+        <v>-0.3038002717171717</v>
+      </c>
+      <c r="K38" s="47" t="n">
+        <v>-0.3696208377037562</v>
+      </c>
+      <c r="L38" s="47" t="n">
+        <v>-0.2918899332657201</v>
+      </c>
+      <c r="M38" s="60" t="n">
+        <v>3.237580904797172</v>
+      </c>
+      <c r="N38" s="57" t="n">
+        <v>-6.582056598658453</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>886856687067</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>大骨</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面牛系列大骨牛肉味方便面食品泡面拉面汤面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D39" s="47" t="n">
+        <v>-0.002803777594728172</v>
+      </c>
+      <c r="E39" s="37" t="n">
+        <v>0.006073942491142001</v>
+      </c>
+      <c r="F39" s="47" t="n">
+        <v>-0.0294586348570061</v>
+      </c>
+      <c r="G39" s="47" t="n">
+        <v>-0.141612670491321</v>
+      </c>
+      <c r="H39" s="37" t="n">
+        <v>0.01537775778949531</v>
+      </c>
+      <c r="I39" s="37" t="n">
+        <v>0.06172282180113561</v>
+      </c>
+      <c r="J39" s="37" t="n">
+        <v>0.1172526417368673</v>
+      </c>
+      <c r="K39" s="37" t="n">
+        <v>0.03990878539246889</v>
+      </c>
+      <c r="L39" s="47" t="n">
+        <v>-0.1292732598627787</v>
+      </c>
+      <c r="M39" s="60" t="n">
+        <v>5.552981993573174</v>
+      </c>
+      <c r="N39" s="57" t="n">
+        <v>-7.734385634439846</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>976466902934</t>
+        </is>
+      </c>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>日韩杯面</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>【天猫U选】indomie营多捞面辣火鸡味日式鸡肉原味杯面</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="n">
+        <v>-0.543884052183466</v>
+      </c>
+      <c r="E40" s="47" t="n">
+        <v>-0.3033023578456758</v>
+      </c>
+      <c r="F40" s="47" t="n">
+        <v>-0.4020667958532695</v>
+      </c>
+      <c r="G40" s="47" t="n">
+        <v>-0.391625092126958</v>
+      </c>
+      <c r="H40" s="47" t="n">
+        <v>-0.3847576543878656</v>
+      </c>
+      <c r="I40" s="47" t="n">
+        <v>-0.6362916999999999</v>
+      </c>
+      <c r="J40" s="47" t="n">
+        <v>-0.4342751608938547</v>
+      </c>
+      <c r="K40" s="47" t="n">
+        <v>-0.3134393233898305</v>
+      </c>
+      <c r="L40" s="37" t="n"/>
+      <c r="M40" s="60" t="n">
+        <v>20.20165391061452</v>
+      </c>
+      <c r="N40" s="60" t="n">
+        <v>12.08358375040242</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>971242260371</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>韩式袋面</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>新品营多捞面韩式辣蘑菇汤面泡面方便面速食干拌面宿舍宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D41" s="37" t="n">
+        <v>0.0129804053430713</v>
+      </c>
+      <c r="E41" s="47" t="n">
+        <v>-1.299296489957395</v>
+      </c>
+      <c r="F41" s="47" t="n">
+        <v>-0.1619325435052057</v>
+      </c>
+      <c r="G41" s="47" t="n">
+        <v>-0.1850412048114185</v>
+      </c>
+      <c r="H41" s="47" t="n">
+        <v>-0.112239251712961</v>
+      </c>
+      <c r="I41" s="47" t="n">
+        <v>-0.4503419801782626</v>
+      </c>
+      <c r="J41" s="47" t="n">
+        <v>-0.2219027006098687</v>
+      </c>
+      <c r="K41" s="47" t="n">
+        <v>-0.1230514543681034</v>
+      </c>
+      <c r="L41" s="47" t="n">
+        <v>-0.1275424751442934</v>
+      </c>
+      <c r="M41" s="60" t="n">
+        <v>22.84392795683939</v>
+      </c>
+      <c r="N41" s="60" t="n">
+        <v>9.885124624176536</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>903183018417</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>七口味混搭</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>进口营多捞面汤面拌面七口味混合方便面速拉面宿舍拌面泡面食食品</t>
+        </is>
+      </c>
+      <c r="D42" s="47" t="n">
+        <v>-0.1456350243770314</v>
+      </c>
+      <c r="E42" s="47" t="n">
+        <v>-0.2448704527845036</v>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>0.08519397972116603</v>
+      </c>
+      <c r="G42" s="47" t="n">
+        <v>-0.04596030204183266</v>
+      </c>
+      <c r="H42" s="47" t="n">
+        <v>-0.03122278401360544</v>
+      </c>
+      <c r="I42" s="47" t="n">
+        <v>-0.5322161411905474</v>
+      </c>
+      <c r="J42" s="47" t="n">
+        <v>-0.2612315660137369</v>
+      </c>
+      <c r="K42" s="47" t="n">
+        <v>-0.06957129562043796</v>
+      </c>
+      <c r="L42" s="37" t="n">
+        <v>0.008530042371433452</v>
+      </c>
+      <c r="M42" s="60" t="n">
+        <v>27.09845751768105</v>
+      </c>
+      <c r="N42" s="60" t="n">
+        <v>19.16602703932989</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>1014512281808</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面韩式甜辣炸鸡辣蘑菇杯面方便面拌面泡面宿舍速食面</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="37" t="n"/>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="37" t="n">
+        <v>0.1884973216342692</v>
+      </c>
+      <c r="J43" s="37" t="n"/>
+      <c r="K43" s="37" t="n"/>
+      <c r="L43" s="37" t="n"/>
+      <c r="M43" s="60" t="n"/>
+      <c r="N43" s="60" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>1019397839311</t>
+        </is>
+      </c>
+      <c r="B44" s="42" t="inlineStr">
+        <is>
+          <t>多口味混搭</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面原味番茄牛肉袋装泡面汤面干拌面方便面宿舍速食旅行宵夜</t>
+        </is>
+      </c>
+      <c r="D44" s="47" t="n">
+        <v>-0.1335403832960477</v>
+      </c>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="37" t="n"/>
+      <c r="J44" s="37" t="n"/>
+      <c r="K44" s="37" t="n"/>
+      <c r="L44" s="37" t="n"/>
+      <c r="M44" s="60" t="n"/>
+      <c r="N44" s="60" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>1040679932754</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>印尼进口营多捞面杯面原味甜辣蘑菇味整箱速食拌面拉面泡面方便面</t>
+        </is>
+      </c>
+      <c r="D45" s="47" t="n">
+        <v>-0.220633405034325</v>
+      </c>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="37" t="n"/>
+      <c r="G45" s="37" t="n"/>
+      <c r="H45" s="47" t="n">
+        <v>-0.1354487803875514</v>
+      </c>
+      <c r="I45" s="37" t="n"/>
+      <c r="J45" s="37" t="n"/>
+      <c r="K45" s="37" t="n"/>
+      <c r="L45" s="37" t="n"/>
+      <c r="M45" s="60" t="n"/>
+      <c r="N45" s="60" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>1056927747753</t>
+        </is>
+      </c>
+      <c r="B46" s="42" t="inlineStr">
+        <is>
+          <t>巴东</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
+        </is>
+      </c>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="47" t="n">
+        <v>-0.2167289594484996</v>
+      </c>
+      <c r="G46" s="37" t="n"/>
+      <c r="H46" s="37" t="n"/>
+      <c r="I46" s="37" t="n"/>
+      <c r="J46" s="37" t="n"/>
+      <c r="K46" s="37" t="n"/>
+      <c r="L46" s="37" t="n"/>
+      <c r="M46" s="60" t="n"/>
+      <c r="N46" s="60" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>1067350828719</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="inlineStr"/>
+      <c r="C47" s="42" t="inlineStr"/>
+      <c r="D47" s="37" t="n"/>
+      <c r="E47" s="37" t="n"/>
+      <c r="F47" s="37" t="n"/>
+      <c r="G47" s="37" t="n"/>
+      <c r="H47" s="37" t="n"/>
+      <c r="I47" s="37" t="n"/>
+      <c r="J47" s="37" t="n"/>
+      <c r="K47" s="37" t="n">
+        <v>0.1918013517148622</v>
+      </c>
+      <c r="L47" s="37" t="n"/>
+      <c r="M47" s="60" t="n"/>
+      <c r="N47" s="60" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>1067363868298</t>
+        </is>
+      </c>
+      <c r="B48" s="42" t="inlineStr"/>
+      <c r="C48" s="42" t="inlineStr"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
+      <c r="K48" s="47" t="n">
+        <v>-0.04877350676110753</v>
+      </c>
+      <c r="L48" s="37" t="n"/>
+      <c r="M48" s="60" t="n"/>
+      <c r="N48" s="60" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>1067957289054</t>
+        </is>
+      </c>
+      <c r="B49" s="42" t="inlineStr">
+        <is>
+          <t>巴东牛肉</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
+        </is>
+      </c>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="37" t="n"/>
+      <c r="G49" s="37" t="n"/>
+      <c r="H49" s="37" t="n"/>
+      <c r="I49" s="37" t="n"/>
+      <c r="J49" s="37" t="n"/>
+      <c r="K49" s="47" t="n">
+        <v>-0.09165839307401936</v>
+      </c>
+      <c r="L49" s="47" t="n">
+        <v>-0.1748460284541724</v>
+      </c>
+      <c r="M49" s="60" t="n"/>
+      <c r="N49" s="60" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>754828376158</t>
+        </is>
+      </c>
+      <c r="B50" s="42" t="inlineStr">
+        <is>
+          <t>六口味混搭</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>进口营多捞面汤面拌面六口味混合方便面速食食品泡面</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="n">
+        <v>-0.1037823210175651</v>
+      </c>
+      <c r="E50" s="47" t="n">
+        <v>-0.00529735976331361</v>
+      </c>
+      <c r="F50" s="37" t="n"/>
+      <c r="G50" s="37" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="37" t="n"/>
+      <c r="J50" s="37" t="n"/>
+      <c r="K50" s="37" t="n"/>
+      <c r="L50" s="37" t="n"/>
+      <c r="M50" s="60" t="n"/>
+      <c r="N50" s="60" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>773972883430</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="inlineStr">
+        <is>
+          <t>韩式袋面</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面韩式火鸡面辣蘑菇汤面袋装泡面辣味速食方便面宿舍宵夜面</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="n">
+        <v>-0.7914333460317459</v>
+      </c>
+      <c r="E51" s="37" t="n">
+        <v>0.06658463765467983</v>
+      </c>
+      <c r="F51" s="37" t="n">
+        <v>0.0006367563180404354</v>
+      </c>
+      <c r="G51" s="37" t="n">
+        <v>0.02133440160614028</v>
+      </c>
+      <c r="H51" s="47" t="n">
+        <v>-0.07410826984126982</v>
+      </c>
+      <c r="I51" s="37" t="n"/>
+      <c r="J51" s="37" t="n"/>
+      <c r="K51" s="37" t="n"/>
+      <c r="L51" s="37" t="n"/>
+      <c r="M51" s="60" t="n"/>
+      <c r="N51" s="60" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>869217868453</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t>韩式杯面</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面韩式甜辣炸鸡辣蘑菇杯面方便面拌面泡面宿舍速食面</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="n">
+        <v>-0.5541078332260142</v>
+      </c>
+      <c r="E52" s="47" t="n">
+        <v>-0.04453104</v>
+      </c>
+      <c r="F52" s="37" t="n"/>
+      <c r="G52" s="37" t="n">
+        <v>0.02546734669338677</v>
+      </c>
+      <c r="H52" s="47" t="n">
+        <v>-0.3123713944954128</v>
+      </c>
+      <c r="I52" s="37" t="n">
+        <v>0.06429885279096854</v>
+      </c>
+      <c r="J52" s="37" t="n"/>
+      <c r="K52" s="47" t="n">
+        <v>-0.4998859813967673</v>
+      </c>
+      <c r="L52" s="47" t="n">
+        <v>-0.06663491022085259</v>
+      </c>
+      <c r="M52" s="60" t="n"/>
+      <c r="N52" s="60" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>949962665617</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>韩式袋面</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面韩式火鸡面辣蘑菇汤面袋装泡面辣味速食方便面宿舍宵夜面</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="n">
+        <v>-0.3864925771464558</v>
+      </c>
+      <c r="E53" s="47" t="n">
+        <v>-0.7442433277709301</v>
+      </c>
+      <c r="F53" s="47" t="n">
+        <v>-0.7076507160734148</v>
+      </c>
+      <c r="G53" s="37" t="n"/>
+      <c r="H53" s="47" t="n">
+        <v>-0.4324761949653223</v>
+      </c>
+      <c r="I53" s="47" t="n">
+        <v>-0.8103794999999999</v>
+      </c>
+      <c r="J53" s="37" t="n"/>
+      <c r="K53" s="37" t="n"/>
+      <c r="L53" s="37" t="n"/>
+      <c r="M53" s="60" t="n"/>
+      <c r="N53" s="60" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>965545088099</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>十口味混搭</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>营多捞面多口味袋装泡面拌面速食面干拌面方便面速食宵夜宿舍旅行</t>
+        </is>
+      </c>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="37" t="n">
+        <v>0.2262198618116698</v>
+      </c>
+      <c r="F54" s="37" t="n"/>
+      <c r="G54" s="37" t="n"/>
+      <c r="H54" s="37" t="n">
+        <v>0.2415521666666667</v>
+      </c>
+      <c r="I54" s="37" t="n"/>
+      <c r="J54" s="37" t="n"/>
+      <c r="K54" s="37" t="n"/>
+      <c r="L54" s="37" t="n">
+        <v>0.1809117269120914</v>
+      </c>
+      <c r="M54" s="60" t="n"/>
+      <c r="N54" s="60" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>975092562679</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>杯面混搭</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>营多韩式甜辣炸鸡火鸡面辣蘑菇杯面拌面泡面方便面速食宵夜旅行</t>
+        </is>
+      </c>
+      <c r="D55" s="37" t="n"/>
+      <c r="E55" s="37" t="n">
+        <v>0.1029609000423549</v>
+      </c>
+      <c r="F55" s="37" t="n">
+        <v>0.2602663309075342</v>
+      </c>
+      <c r="G55" s="47" t="n">
+        <v>-0.02685346950171821</v>
+      </c>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="37" t="n"/>
+      <c r="J55" s="37" t="n"/>
+      <c r="K55" s="37" t="n">
+        <v>0.1606794672172594</v>
+      </c>
+      <c r="L55" s="37" t="n"/>
+      <c r="M55" s="60" t="n"/>
+      <c r="N55" s="60" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>976535014785</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr"/>
+      <c r="C56" s="42" t="inlineStr"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="37" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="37" t="n"/>
+      <c r="J56" s="37" t="n"/>
+      <c r="K56" s="47" t="n">
+        <v>-1.512805017467249</v>
+      </c>
+      <c r="L56" s="37" t="n"/>
+      <c r="M56" s="60" t="n"/>
+      <c r="N56" s="60" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:N56"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44931,143 +48827,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="40" t="inlineStr">
-        <is>
-          <t>周次</t>
-        </is>
-      </c>
-      <c r="B1" s="40" t="inlineStr">
-        <is>
-          <t>周报其他费用</t>
-        </is>
-      </c>
-      <c r="C1" s="40" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>5.11-5.17</t>
-        </is>
-      </c>
-      <c r="B2" s="29" t="n">
-        <v>1911</v>
-      </c>
-      <c r="C2" s="36" t="inlineStr">
-        <is>
-          <t>数据源1「其他费用」= 本表费用 × 当周件数占比（已写入数值，避免打开为0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>5.25-5.31</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="n">
-        <v>1911</v>
-      </c>
-      <c r="C3" s="36" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>6.15-6.21</t>
-        </is>
-      </c>
-      <c r="B4" s="29" t="n">
-        <v>3605</v>
-      </c>
-      <c r="C4" s="36" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>6.22-6.28</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="n">
-        <v>3605</v>
-      </c>
-      <c r="C5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>6.29-7.5</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="n">
-        <v>1951</v>
-      </c>
-      <c r="C6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>7.6-7.12</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>2054</v>
-      </c>
-      <c r="C7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>7.13-7.19</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="n">
-        <v>2405</v>
-      </c>
-      <c r="C8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>7.20-7.26</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>2097</v>
-      </c>
-      <c r="C9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>7.27-8.2</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>2127</v>
-      </c>
-      <c r="C10" s="36" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
+++ b/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -331,6 +331,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +500,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1684,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2176,47 +2178,47 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>定位</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>前周利率</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="61" t="inlineStr">
         <is>
           <t>后周利率</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="61" t="inlineStr">
         <is>
           <t>利率变化(pp)</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="G35" s="61" t="inlineStr">
         <is>
           <t>前利率变化(pp)</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
+      <c r="H35" s="61" t="inlineStr">
         <is>
           <t>费率变化(pp)</t>
         </is>
       </c>
-      <c r="I35" s="26" t="inlineStr">
+      <c r="I35" s="61" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
@@ -2233,7 +2235,7 @@
       </c>
       <c r="C36" s="42" t="inlineStr">
         <is>
-          <t>巴东牛肉</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D36" s="47" t="n">
@@ -2268,7 +2270,7 @@
       </c>
       <c r="C37" s="42" t="inlineStr">
         <is>
-          <t>巴东牛肉</t>
+          <t>12包</t>
         </is>
       </c>
       <c r="D37" s="37" t="n">
@@ -2373,7 +2375,7 @@
       </c>
       <c r="C40" s="42" t="inlineStr">
         <is>
-          <t>巴东牛肉</t>
+          <t>30包</t>
         </is>
       </c>
       <c r="D40" s="37" t="n">
@@ -2408,7 +2410,7 @@
       </c>
       <c r="C41" s="42" t="inlineStr">
         <is>
-          <t>15包</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D41" s="37" t="n">
@@ -2502,6 +2504,8 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="56" t="inlineStr">
         <is>
@@ -2510,47 +2514,47 @@
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="61" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C47" s="61" t="inlineStr">
         <is>
           <t>定位</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="61" t="inlineStr">
         <is>
           <t>前周利率</t>
         </is>
       </c>
-      <c r="E47" s="26" t="inlineStr">
+      <c r="E47" s="61" t="inlineStr">
         <is>
           <t>后周利率</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="F47" s="61" t="inlineStr">
         <is>
           <t>利率变化(pp)</t>
         </is>
       </c>
-      <c r="G47" s="26" t="inlineStr">
+      <c r="G47" s="61" t="inlineStr">
         <is>
           <t>前利率变化(pp)</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="H47" s="61" t="inlineStr">
         <is>
           <t>费率变化(pp)</t>
         </is>
       </c>
-      <c r="I47" s="26" t="inlineStr">
+      <c r="I47" s="61" t="inlineStr">
         <is>
           <t>原因</t>
         </is>
@@ -2567,7 +2571,7 @@
       </c>
       <c r="C48" s="42" t="inlineStr">
         <is>
-          <t>混搭5杯</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D48" s="47" t="n">
@@ -2637,7 +2641,7 @@
       </c>
       <c r="C50" s="42" t="inlineStr">
         <is>
-          <t>巴东牛肉</t>
+          <t>30包</t>
         </is>
       </c>
       <c r="D50" s="47" t="n">
@@ -2672,7 +2676,7 @@
       </c>
       <c r="C51" s="42" t="inlineStr">
         <is>
-          <t>24包</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D51" s="47" t="n">
@@ -2707,7 +2711,7 @@
       </c>
       <c r="C52" s="42" t="inlineStr">
         <is>
-          <t>15包</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D52" s="47" t="n">
@@ -2742,7 +2746,7 @@
       </c>
       <c r="C53" s="42" t="inlineStr">
         <is>
-          <t>日式袋面</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="D53" s="47" t="n">
@@ -2836,16 +2840,55 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>注：绝对利润额上，7.6→7.13 更像「推广前利润下降」（成交掉）；利率口径下同期「推广费率」抬升更明显。两套口径都要看：额看规模，利率看单位赚钱能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A46:I46"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A34:I34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3348,8 +3391,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
+++ b/天猫近3月数据_分析结果/天猫利润分析_领导汇报.xlsx
@@ -297,7 +297,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -386,7 +385,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -7988,10 +7986,17 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>一致性提醒：同源周表存在同一商品ID跨周改挂品类（如30包ID在某周记为巴东）。ID利润可加总；按定位专题/同品环比需看当周品名，详见利润分析「08-一致性核对」。</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>本工作簿除标注「输入值」的浅蓝/底色单元格外，金额、利率、环比、差值均为Excel公式。</t>
+          <t>巴东推广费率按周约20%–36%（成交较大周），不宜笼统写成固定32%–38%。</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21458,7 @@
       </c>
       <c r="D113" s="22" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="E113" s="22" t="inlineStr">
@@ -22533,7 +22538,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="E122" s="22" t="inlineStr">
@@ -22893,7 +22898,7 @@
       </c>
       <c r="D125" s="22" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="E125" s="22" t="inlineStr">
@@ -23253,7 +23258,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="E128" s="22" t="inlineStr">
@@ -23373,7 +23378,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="E129" s="22" t="inlineStr">
@@ -24693,7 +24698,7 @@
       </c>
       <c r="D140" s="22" t="inlineStr">
         <is>
-          <t>韩火鸡</t>
+          <t>韩式火鸡</t>
         </is>
       </c>
       <c r="E140" s="22" t="inlineStr">
